--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>YUV&amp;MAYU שיר שלי בשבילך</v>
+        <v>אפרת גוש – סוף סוף אושר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/yuvmayu-%d7%a9%d7%99%d7%a8-%d7%a9%d7%9c%d7%99-%d7%91%d7%a9%d7%91%d7%99%d7%9c%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a4%d7%a8%d7%aa-%d7%92%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a1%d7%95%d7%a3-%d7%90%d7%95%d7%a9%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר הוא בלדה רכה ואינטימית שנכתבה ומבוצעת על ידי מאיה לוי ויובל גז, .צמד יוצרות צעירות שנפגשו בלימודיהן בבית הספר למוזיקה רימון. הבלדה מבטאת כמיהה נאיבית-עדינה לאהבה, ומציירת מצב רגשי של המתנה למפגש עם אדם שעדיין לא נכנס לחיים –</v>
+        <v>השיר שייך לשלב בוגר ביצירתה של אפרת גוש, אך הוא מסופר מנקודת מבט צעירה מאוד – כמעט וידויית. בקליפ, הזמרת צופה בדמות שמגלמת אותה כצעירה בת 19, מה שיוצר דיאלוג בין עבר להווה: האישה הבוגרת מתבוננת על החלומות, הפחדים והשאיפות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>YUV&amp;MAYU שיר שלי בשבילך</v>
+        <v>אפרת גוש – סוף סוף אושר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אפרת גוש – סוף סוף אושר</v>
+        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a4%d7%a8%d7%aa-%d7%92%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a1%d7%95%d7%a3-%d7%90%d7%95%d7%a9%d7%a8/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409912&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר שייך לשלב בוגר ביצירתה של אפרת גוש, אך הוא מסופר מנקודת מבט צעירה מאוד – כמעט וידויית. בקליפ, הזמרת צופה בדמות שמגלמת אותה כצעירה בת 19, מה שיוצר דיאלוג בין עבר להווה: האישה הבוגרת מתבוננת על החלומות, הפחדים והשאיפות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,354 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אפרת גוש – סוף סוף אושר</v>
+        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>נתנאל ששון - זה רשמי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409911&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>נתנאל ששון - זה רשמי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נתנאל אבקסיס - אין שום יאוש</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409910&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נתנאל אבקסיס - אין שום יאוש</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409909&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409908&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מאיר רובין - הפצע בלב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409907&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מאיר רובין - הפצע בלב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>טליה אלפסי - מדבר ושותק</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409906&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>טליה אלפסי - מדבר ושותק</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>חגית אסולין - שמש כבויה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409905&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>חגית אסולין - שמש כבויה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409904&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אבישי - מזמור לתודה</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409903&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-08</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אבישי - מזמור לתודה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
+        <v>נתנאל ששון – זה רשמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409912&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
+        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%a0%d7%90%d7%9c-%d7%a9%d7%a9%d7%95%d7%9f-%d7%96%d7%94-%d7%a8%d7%a9%d7%9e%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>נתנאל ששון שר בלדה ים-תיכונית טיפוסית על אהבה שנגמרה, שמנסה לשלב בין הצהרה של התגברות לבין רגש שלא באמת נעלם. כבר משם השיר ברור שהדובר מבקש להכריז על סיום סופי,  אבל ככל שמתקדמים בטקסט ובביצוע הקולי, נוצר הרושם שהסיום הזה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,354 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שי גז &amp; אברהם לוי - חדש בכל רגע</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>נתנאל ששון - זה רשמי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409911&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>נתנאל ששון - זה רשמי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נתנאל אבקסיס - אין שום יאוש</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409910&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נתנאל אבקסיס - אין שום יאוש</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409909&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>נועם בתן - Michelle - השיר הרשמי של אירוויזיון 2026</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409908&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>נהוראי רחמימוב &amp; אריאל מויאל - בוא ונרקוד</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>מאיר רובין - הפצע בלב</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409907&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>מאיר רובין - הפצע בלב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>טליה אלפסי - מדבר ושותק</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409906&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>טליה אלפסי - מדבר ושותק</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>חגית אסולין - שמש כבויה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409905&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>חגית אסולין - שמש כבויה</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409904&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אורי אילן סבח - מחרוזת סוד האהבה 2026</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אבישי - מזמור לתודה</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409903&amp;sid=9f3847199a1478c7dbbc018aa914d2d9</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-08</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אבישי - מזמור לתודה</v>
+        <v>נתנאל ששון – זה רשמי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נתנאל ששון – זה רשמי</v>
+        <v>מיקה משה &amp; הלהקות הצבאיות - אומץ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%a0%d7%90%d7%9c-%d7%a9%d7%a9%d7%95%d7%9f-%d7%96%d7%94-%d7%a8%d7%a9%d7%9e%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409931&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>נתנאל ששון שר בלדה ים-תיכונית טיפוסית על אהבה שנגמרה, שמנסה לשלב בין הצהרה של התגברות לבין רגש שלא באמת נעלם. כבר משם השיר ברור שהדובר מבקש להכריז על סיום סופי,  אבל ככל שמתקדמים בטקסט ובביצוע הקולי, נוצר הרושם שהסיום הזה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,696 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נתנאל ששון – זה רשמי</v>
+        <v>מיקה משה &amp; הלהקות הצבאיות - אומץ</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>להקת דרך - מונולוג מדינה ויראלי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409930&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>להקת דרך - מונולוג מדינה ויראלי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דניאל זנדאני - יא יומה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409929&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דניאל זנדאני - יא יומה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>פיקאסו - מתערבב לי</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409928&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>פיקאסו - מתערבב לי</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>עמרי וקנין - שיר שלא נגמר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409927&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>עמרי וקנין - שיר שלא נגמר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>נעם שפייר - כנות</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409926&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>נעם שפייר - כנות</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ישי ריבו - הנשמה לא Meta</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409925&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ישי ריבו - הנשמה לא Meta</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יחיאל ליכטיגר - חוזרים לאבא</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409924&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יחיאל ליכטיגר - חוזרים לאבא</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>יונתן שחר - דרך לחזור</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409923&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>יונתן שחר - דרך לחזור</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>יוחאי בן אב"י - וארשתיך לי</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409922&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>יוחאי בן אב"י - וארשתיך לי</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יובל אבידן - ברוך השם אני טוב</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409921&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יובל אבידן - ברוך השם אני טוב</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>חני מסלה - פאבלות</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409920&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>חני מסלה - פאבלות</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>הילה גדסי - רק אתה יודע</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409919&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>הילה גדסי - רק אתה יודע</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>האחים בכר - נשאר הגעגוע</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409918&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>האחים בכר - נשאר הגעגוע</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>דניאל כהן - ימים של גאולה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409917&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>דניאל כהן - ימים של גאולה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>דילן דרור &amp; ויק אוחנה - יד על הלב</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409916&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>דילן דרור &amp; ויק אוחנה - יד על הלב</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>דוד חיים - מחרוזת שירי פורים 2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409915&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>דוד חיים - מחרוזת שירי פורים 2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>בנאל בן ציון - שיכור עם געגוע</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409914&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>בנאל בן ציון - שיכור עם געגוע</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>בן זוהר - טיל</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409913&amp;sid=df4c3d4a5c70338b67ab2495eebc8a17</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-03-09</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>בן זוהר - טיל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל אבידן – ברוך השם אני טוב</v>
+        <v>שמעון לוי &amp; עמירן דביר - להיות אהוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%90%d7%91%d7%99%d7%93%d7%9f-%d7%91%d7%a8%d7%95%d7%9a-%d7%94%d7%a9%d7%9d-%d7%90%d7%a0%d7%99-%d7%98%d7%95%d7%91/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409951&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יובל אבידן שר  שיר אמוני-אישי שמציג תהליך של חזרה פנימה וחיזוק רוחני. הוא כתוב בשפה פשוטה וישירה, עם מנגינה קליטה וקצב מיד-טמפו רגוע, ללא שיא דרמטי גדול – דבר שמשרת את המסר הפנימי והמתון של השיר. השיר מתאר תהליך של</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,354 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל אבידן – ברוך השם אני טוב</v>
+        <v>שמעון לוי &amp; עמירן דביר - להיות אהוב</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שמעון לוי - אהבת השם</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409950&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שמעון לוי - אהבת השם</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>רפא' - יהודי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409949&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>רפא' - יהודי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ריעות זלאיט - חלום</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409948&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ריעות זלאיט - חלום</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>סאליאור פטיטו - בין הכיסאות</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409947&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>סאליאור פטיטו - בין הכיסאות</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ליאם גולן - להיות רק בשמחה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409946&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>ליאם גולן - להיות רק בשמחה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יוסי פריד - מחרוזת שבת 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409945&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יוסי פריד - מחרוזת שבת 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אורן כדורי - אמא מה עושים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409944&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אורן כדורי - אמא מה עושים</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אופיר אלחייני - שדה שושנים</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409943&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אופיר אלחייני - שדה שושנים</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אברימי רוט - יצא אדם</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409942&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-10</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אברימי רוט - יצא אדם</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון לוי &amp; עמירן דביר - להיות אהוב</v>
+        <v>נועה פארן &amp; אביחי טוכמן – זז באדמה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409951&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a4%d7%90%d7%a8%d7%9f-%d7%90%d7%91%d7%99%d7%97%d7%99-%d7%98%d7%95%d7%9b%d7%9e%d7%9f-%d7%96%d7%96-%d7%91%d7%90%d7%93%d7%9e%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר של נועה פארן (בביצוע) ואביחי טוכמן (יוצר/מפיק) פועל כמו ניסיון מודע ליצור מרחב קטן של חופש בתוך הרעש העירוני. זהו פופ קליט עם בסיס קצבי שמושפע מרגאטון, כמעט שיר מדיטטיבי במסווה של שיר רחבה. השיר מתאר רגע שבו המוזיקה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,354 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון לוי &amp; עמירן דביר - להיות אהוב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שמעון לוי - אהבת השם</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409950&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שמעון לוי - אהבת השם</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רפא' - יהודי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409949&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רפא' - יהודי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ריעות זלאיט - חלום</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409948&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>ריעות זלאיט - חלום</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>סאליאור פטיטו - בין הכיסאות</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409947&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>סאליאור פטיטו - בין הכיסאות</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ליאם גולן - להיות רק בשמחה</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409946&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ליאם גולן - להיות רק בשמחה</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>יוסי פריד - מחרוזת שבת 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409945&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>יוסי פריד - מחרוזת שבת 2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אורן כדורי - אמא מה עושים</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409944&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אורן כדורי - אמא מה עושים</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>אופיר אלחייני - שדה שושנים</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409943&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>אופיר אלחייני - שדה שושנים</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אברימי רוט - יצא אדם</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409942&amp;sid=c993e7361615b1dd2d8db723e753315e</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אברימי רוט - יצא אדם</v>
+        <v>נועה פארן &amp; אביחי טוכמן – זז באדמה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה פארן &amp; אביחי טוכמן – זז באדמה</v>
+        <v>מיקה משה והלהקות הצבאיות – אומץ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a4%d7%90%d7%a8%d7%9f-%d7%90%d7%91%d7%99%d7%97%d7%99-%d7%98%d7%95%d7%9b%d7%9e%d7%9f-%d7%96%d7%96-%d7%91%d7%90%d7%93%d7%9e%d7%94/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%9e%d7%a9%d7%94-%d7%95%d7%94%d7%9c%d7%94%d7%a7%d7%95%d7%aa-%d7%94%d7%a6%d7%91%d7%90%d7%99%d7%95%d7%aa-%d7%90%d7%95%d7%9e%d7%a5/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-11</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר של נועה פארן (בביצוע) ואביחי טוכמן (יוצר/מפיק) פועל כמו ניסיון מודע ליצור מרחב קטן של חופש בתוך הרעש העירוני. זהו פופ קליט עם בסיס קצבי שמושפע מרגאטון, כמעט שיר מדיטטיבי במסווה של שיר רחבה. השיר מתאר רגע שבו המוזיקה</v>
+        <v>השיר “אומץ” בביצוע של מיקה משה עם הלהקות הצבאיות של צה״ל הוא שיר פופ מלודי שמנסה להיות המנון עידוד לנשים בתקופת מלחמה. הוא משתמש במוזיקה רכה ומחבקת כדי להעביר מסר של כוח, עמידה ותקווה. מצד אחד הוא יעיל רגשית ופונה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה פארן &amp; אביחי טוכמן – זז באדמה</v>
+        <v>מיקה משה והלהקות הצבאיות – אומץ</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקה משה והלהקות הצבאיות – אומץ</v>
+        <v>אלחנן ענבל - מלאך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%9e%d7%a9%d7%94-%d7%95%d7%94%d7%9c%d7%94%d7%a7%d7%95%d7%aa-%d7%94%d7%a6%d7%91%d7%90%d7%99%d7%95%d7%aa-%d7%90%d7%95%d7%9e%d7%a5/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409958&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-11</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “אומץ” בביצוע של מיקה משה עם הלהקות הצבאיות של צה״ל הוא שיר פופ מלודי שמנסה להיות המנון עידוד לנשים בתקופת מלחמה. הוא משתמש במוזיקה רכה ומחבקת כדי להעביר מסר של כוח, עמידה ותקווה. מצד אחד הוא יעיל רגשית ופונה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,240 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקה משה והלהקות הצבאיות – אומץ</v>
+        <v>אלחנן ענבל - מלאך</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>איציק דדיה - יצר טוב</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409957&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>איציק דדיה - יצר טוב</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אייל סאלם - מחשבות</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409956&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אייל סאלם - מחשבות</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אור שושן &amp; מור סופר - זמן</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409955&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אור שושן &amp; מור סופר - זמן</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אברימי רוט - בשם המלך</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409954&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אברימי רוט - בשם המלך</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אבי ביטר - לא מפחדים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409953&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אבי ביטר - לא מפחדים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Pure Spirit - מתגעגעת</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409952&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-11</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>Pure Spirit - מתגעגעת</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלחנן ענבל - מלאך</v>
+        <v>שירז אברהם - אבא תודה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409958&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409965&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-11</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלחנן ענבל - מלאך</v>
+        <v>שירז אברהם - אבא תודה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>איציק דדיה - יצר טוב</v>
+        <v>עמרי אלשוקני - מאשאפ שנות ה 90</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409957&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409964&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-11</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>איציק דדיה - יצר טוב</v>
+        <v>עמרי אלשוקני - מאשאפ שנות ה 90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אייל סאלם - מחשבות</v>
+        <v>משה קליין &amp; דוד חפצדי - ואיך הימים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409956&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409963&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-11</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אייל סאלם - מחשבות</v>
+        <v>משה קליין &amp; דוד חפצדי - ואיך הימים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אור שושן &amp; מור סופר - זמן</v>
+        <v>להקת דרך - אל תאמר</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409955&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409962&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-11</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אור שושן &amp; מור סופר - זמן</v>
+        <v>להקת דרך - אל תאמר</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אברימי רוט - בשם המלך</v>
+        <v>יצחק אפרים קוך - ואני בחסדך בטחתי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409954&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409961&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-11</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אברימי רוט - בשם המלך</v>
+        <v>יצחק אפרים קוך - ואני בחסדך בטחתי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אבי ביטר - לא מפחדים</v>
+        <v>יניב בן ישי - זאב בודד</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409953&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409960&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-11</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אבי ביטר - לא מפחדים</v>
+        <v>יניב בן ישי - זאב בודד</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Pure Spirit - מתגעגעת</v>
+        <v>הרב יהודה חודדה - לכבוד חמדת לבבי 2026</v>
       </c>
       <c r="B8" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409952&amp;sid=19f2269f6a7663d13b7ea33c9809090c</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409959&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-11</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Pure Spirit - מתגעגעת</v>
+        <v>הרב יהודה חודדה - לכבוד חמדת לבבי 2026</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שירז אברהם - אבא תודה</v>
+        <v>אור עמרמי ברוקמן – תמיד חוזר למנגינה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409965&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a2%d7%9e%d7%a8%d7%9e%d7%99-%d7%91%d7%a8%d7%95%d7%a7%d7%9e%d7%9f-%d7%aa%d7%9e%d7%99%d7%93-%d7%97%d7%95%d7%96%d7%a8-%d7%9c%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>אור עמרמי ברוקמן שר שיר פופ שמח ופשוט לכאורה, אך בהקשר שבו נכתב – בזמן שהזמר שהה במקלטים במהלך מלחמת מלחמת שאגת הארי – הוא מקבל משמעות עמוקה יותר: המוזיקה ככלי הישרדות רגשי. השיר מתאר ניסיון לשמור על שגרה ואופטימיות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,240 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שירז אברהם - אבא תודה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>עמרי אלשוקני - מאשאפ שנות ה 90</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409964&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>עמרי אלשוקני - מאשאפ שנות ה 90</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>משה קליין &amp; דוד חפצדי - ואיך הימים</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409963&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>משה קליין &amp; דוד חפצדי - ואיך הימים</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>להקת דרך - אל תאמר</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409962&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>להקת דרך - אל תאמר</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יצחק אפרים קוך - ואני בחסדך בטחתי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409961&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יצחק אפרים קוך - ואני בחסדך בטחתי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>יניב בן ישי - זאב בודד</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409960&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>יניב בן ישי - זאב בודד</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>הרב יהודה חודדה - לכבוד חמדת לבבי 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409959&amp;sid=c58b90bdfe7aee15dc200715dd0102e0</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>הרב יהודה חודדה - לכבוד חמדת לבבי 2026</v>
+        <v>אור עמרמי ברוקמן – תמיד חוזר למנגינה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אור עמרמי ברוקמן – תמיד חוזר למנגינה</v>
+        <v>ג'יין בורדו – חלמתי שאתה פה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a2%d7%9e%d7%a8%d7%9e%d7%99-%d7%91%d7%a8%d7%95%d7%a7%d7%9e%d7%9f-%d7%aa%d7%9e%d7%99%d7%93-%d7%97%d7%95%d7%96%d7%a8-%d7%9c%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%9f-%d7%91%d7%95%d7%a8%d7%93%d7%95-%d7%97%d7%9c%d7%9e%d7%aa%d7%99-%d7%a9%d7%90%d7%aa%d7%94-%d7%a4%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-12</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אור עמרמי ברוקמן שר שיר פופ שמח ופשוט לכאורה, אך בהקשר שבו נכתב – בזמן שהזמר שהה במקלטים במהלך מלחמת מלחמת שאגת הארי – הוא מקבל משמעות עמוקה יותר: המוזיקה ככלי הישרדות רגשי. השיר מתאר ניסיון לשמור על שגרה ואופטימיות</v>
+        <v>דורון טלמון שרה  בלדה פולק-אקוסטית שקטה אך טעונה מאוד רגשית. היא נע בין שני צירים: חלום אישי על אדם חסר לבין אמירה דורית על צעירים שחיים בתוך מציאות של מלחמות מתמשכות. אחד האלמנטים הבולטים בו הוא ההדהוד ליצירה הקלאסית שיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אור עמרמי ברוקמן – תמיד חוזר למנגינה</v>
+        <v>ג'יין בורדו – חלמתי שאתה פה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'יין בורדו – חלמתי שאתה פה</v>
+        <v>דניאל חן - נפש תאומה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%9f-%d7%91%d7%95%d7%a8%d7%93%d7%95-%d7%97%d7%9c%d7%9e%d7%aa%d7%99-%d7%a9%d7%90%d7%aa%d7%94-%d7%a4%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409973&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-12</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>דורון טלמון שרה  בלדה פולק-אקוסטית שקטה אך טעונה מאוד רגשית. היא נע בין שני צירים: חלום אישי על אדם חסר לבין אמירה דורית על צעירים שחיים בתוך מציאות של מלחמות מתמשכות. אחד האלמנטים הבולטים בו הוא ההדהוד ליצירה הקלאסית שיר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'יין בורדו – חלמתי שאתה פה</v>
+        <v>דניאל חן - נפש תאומה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>דנה זר - עוד סיבה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409972&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>דנה זר - עוד סיבה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>גל סבג - מחרוזת ברית 2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409971&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>גל סבג - מחרוזת ברית 2026</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ג’יין בורדו - חלמתי שאתה פה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409970&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ג’יין בורדו - חלמתי שאתה פה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ארז יחיאל &amp; אלחנן בידני - כי אשמרה שבת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409969&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ארז יחיאל &amp; אלחנן בידני - כי אשמרה שבת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>איציק איזמירלי - לא אמרת</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409968&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>איציק איזמירלי - לא אמרת</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אהרן בלעיש - תודה שאתה כאן</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409967&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אהרן בלעיש - תודה שאתה כאן</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אביב סטמס - דמעות על הכרית</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409966&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אביב סטמס - דמעות על הכרית</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דניאל חן - נפש תאומה</v>
+        <v>שמעון בר יוחאי - מחרוזת שירי שבת 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409973&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409980&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-12</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דניאל חן - נפש תאומה</v>
+        <v>שמעון בר יוחאי - מחרוזת שירי שבת 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>דנה זר - עוד סיבה</v>
+        <v>שלום ממן - אהלן וסהלן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409972&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409979&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D3" t="str">
         <v>2026-03-12</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>דנה זר - עוד סיבה</v>
+        <v>שלום ממן - אהלן וסהלן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>גל סבג - מחרוזת ברית 2026</v>
+        <v>עומר יונה - הולכת</v>
       </c>
       <c r="B4" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409971&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409978&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D4" t="str">
         <v>2026-03-12</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>גל סבג - מחרוזת ברית 2026</v>
+        <v>עומר יונה - הולכת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ג’יין בורדו - חלמתי שאתה פה</v>
+        <v>סער ראסטי - תמונה ישנה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409970&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409977&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D5" t="str">
         <v>2026-03-12</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ג’יין בורדו - חלמתי שאתה פה</v>
+        <v>סער ראסטי - תמונה ישנה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ארז יחיאל &amp; אלחנן בידני - כי אשמרה שבת</v>
+        <v>מירי מסיקה - על חוט דק</v>
       </c>
       <c r="B6" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409969&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409976&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D6" t="str">
         <v>2026-03-12</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ארז יחיאל &amp; אלחנן בידני - כי אשמרה שבת</v>
+        <v>מירי מסיקה - על חוט דק</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>איציק איזמירלי - לא אמרת</v>
+        <v>ליאם אוחיון - הלב שלי</v>
       </c>
       <c r="B7" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409968&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409975&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D7" t="str">
         <v>2026-03-12</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>איציק איזמירלי - לא אמרת</v>
+        <v>ליאם אוחיון - הלב שלי</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אהרן בלעיש - תודה שאתה כאן</v>
+        <v>ליאור מזרחי &amp; אלירן צורף - אבא גדול</v>
       </c>
       <c r="B8" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409967&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409974&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
       </c>
       <c r="D8" t="str">
         <v>2026-03-12</v>
@@ -697,50 +697,12 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אהרן בלעיש - תודה שאתה כאן</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביב סטמס - דמעות על הכרית</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409966&amp;sid=9e7b7f175072edda36a8d7e9777610ff</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביב סטמס - דמעות על הכרית</v>
+        <v>ליאור מזרחי &amp; אלירן צורף - אבא גדול</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בר יוחאי - מחרוזת שירי שבת 2026</v>
+        <v>אופיר אלחייני שדה שושנים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409980&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%90%d7%9c%d7%97%d7%99%d7%99%d7%a0%d7%99-%d7%a9%d7%93%d7%94-%d7%a9%d7%95%d7%a9%d7%a0%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר ששר אופיר אלחייני נכתב על רקע הטראומה של מתקפת חמאס על ישראל ב־7 באוקטובר 2023, ובמרכזו עומד דיסוננס בין יופי טבעי לבין הרס אנושי. השיר משתמש בדימויים תנ"כיים, קבליים ופיוטיים כדי לעבד כאב לאומי ולהפוך אותו לתקווה רוחנית. אלחייני</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,240 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בר יוחאי - מחרוזת שירי שבת 2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שלום ממן - אהלן וסהלן</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409979&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שלום ממן - אהלן וסהלן</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>עומר יונה - הולכת</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409978&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>עומר יונה - הולכת</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>סער ראסטי - תמונה ישנה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409977&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>סער ראסטי - תמונה ישנה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מירי מסיקה - על חוט דק</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409976&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מירי מסיקה - על חוט דק</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ליאם אוחיון - הלב שלי</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409975&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>ליאם אוחיון - הלב שלי</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>ליאור מזרחי &amp; אלירן צורף - אבא גדול</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409974&amp;sid=9645bb93739d54b4055bd94c9f8b39ea</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>ליאור מזרחי &amp; אלירן צורף - אבא גדול</v>
+        <v>אופיר אלחייני שדה שושנים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר אלחייני שדה שושנים</v>
+        <v>אופיר אלחייני – שדה שושנים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-14</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר אלחייני שדה שושנים</v>
+        <v>אופיר אלחייני – שדה שושנים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-03-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר אלחייני – שדה שושנים</v>
+        <v>פרחי ירושלים - Ymca</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%90%d7%9c%d7%97%d7%99%d7%99%d7%a0%d7%99-%d7%a9%d7%93%d7%94-%d7%a9%d7%95%d7%a9%d7%a0%d7%99%d7%9d/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410004&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-14</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר ששר אופיר אלחייני נכתב על רקע הטראומה של מתקפת חמאס על ישראל ב־7 באוקטובר 2023, ובמרכזו עומד דיסוננס בין יופי טבעי לבין הרס אנושי. השיר משתמש בדימויים תנ"כיים, קבליים ופיוטיים כדי לעבד כאב לאומי ולהפוך אותו לתקווה רוחנית. אלחייני</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,506 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר אלחייני – שדה שושנים</v>
+        <v>פרחי ירושלים - Ymca</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>סיגלית טואטי - שמח ביוון</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410003&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>סיגלית טואטי - שמח ביוון</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נשמה וקצב - עכשיו זה נגמר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410002&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נשמה וקצב - עכשיו זה נגמר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>משה ברששת - Zina Cover</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410001&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>משה ברששת - Zina Cover</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מאיר חג'בי - היום</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410000&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מאיר חג'בי - היום</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>לידור עמירה - שמעתי שהבית חרב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409999&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>לידור עמירה - שמעתי שהבית חרב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>לידור עמירה - כמה אהבה עצמית</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409998&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>לידור עמירה - כמה אהבה עצמית</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יוסף חיים - בובה על חוט</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409997&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יוסף חיים - בובה על חוט</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Pure Spirit - תן לנו כח - גרסת שאגת הארי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409996&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>Pure Spirit - תן לנו כח - גרסת שאגת הארי</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אלעד מרגי - שוב</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409995&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אלעד מרגי - שוב</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יוסף חיים - הלוואי</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409994&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יוסף חיים - הלוואי</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>דורין פסטרנק - משחקים של כבוד</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409993&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>דורין פסטרנק - משחקים של כבוד</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אביב לוסב - התנשאי לי</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409992&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אביב לוסב - התנשאי לי</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>דניאל חן - נפש תאומה קאבר</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409973&amp;sid=0e7672d7a198bf16a3c5dcff7125218d</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-03-14</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>דניאל חן - נפש תאומה קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
   </ignoredErrors>
 </worksheet>
 </file>